--- a/RDTW_0013_A01_FOC Application Form FOC 申請單_2.xlsx
+++ b/RDTW_0013_A01_FOC Application Form FOC 申請單_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Changc29\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A97D847-2837-46EA-88F4-48E66A3BBEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E06D551-3750-4633-BDFF-DECAAD45B9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1723,13 +1723,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -1741,13 +1734,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -1920,6 +1906,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1956,43 +1962,43 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2010,98 +2016,125 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="28" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2116,65 +2149,38 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="30" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2477,102 +2483,102 @@
       <c r="D1" s="3"/>
     </row>
     <row r="2" spans="1:4" ht="24" customHeight="1">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="62"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="71"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="D3" s="62"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="71"/>
     </row>
     <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="A4" s="60" t="s">
+      <c r="A4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="61"/>
-      <c r="C4" s="61"/>
-      <c r="D4" s="62"/>
+      <c r="B4" s="70"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="71"/>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A5" s="63"/>
-      <c r="B5" s="61"/>
-      <c r="C5" s="61"/>
-      <c r="D5" s="62"/>
+      <c r="A5" s="72"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="71"/>
     </row>
     <row r="6" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="73" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="D6" s="74"/>
+      <c r="D6" s="60"/>
     </row>
     <row r="7" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="75"/>
-      <c r="C7" s="76"/>
-      <c r="D7" s="76"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
     </row>
     <row r="8" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="77" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="78"/>
+      <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="80" t="s">
+      <c r="B9" s="63"/>
+      <c r="C9" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="76"/>
+      <c r="D9" s="66"/>
     </row>
     <row r="10" spans="1:4" ht="34.5" customHeight="1">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="81" t="str">
+      <c r="B10" s="64" t="str">
         <f>IFERROR(VLOOKUP(B9,'FOC Approval Matrix 核准矩陣  '!B:C,2,FALSE),"")</f>
         <v/>
       </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="76"/>
+      <c r="C10" s="65"/>
+      <c r="D10" s="66"/>
     </row>
     <row r="11" spans="1:4" ht="34.5" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="69"/>
-      <c r="C11" s="70" t="s">
+      <c r="B11" s="55"/>
+      <c r="C11" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="71" t="str">
+      <c r="D11" s="57" t="str">
         <f>IFERROR(VLOOKUP(B9,'FOC Approval Matrix 核准矩陣  '!B:D,3,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A12" s="64"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="57"/>
+      <c r="A12" s="75"/>
+      <c r="B12" s="76"/>
+      <c r="C12" s="76"/>
+      <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:4" ht="33.75" customHeight="1">
       <c r="A13" s="4" t="s">
@@ -2614,42 +2620,42 @@
     </row>
     <row r="18" spans="1:4" ht="19.5" customHeight="1">
       <c r="A18" s="7"/>
-      <c r="B18" s="66"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="53"/>
+      <c r="D18" s="53"/>
     </row>
     <row r="19" spans="1:4" ht="57.75" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="9"/>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="52"/>
+      <c r="D19" s="79"/>
     </row>
     <row r="20" spans="1:4" ht="42" customHeight="1">
       <c r="A20" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="53"/>
-      <c r="D20" s="54"/>
+      <c r="B20" s="67"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="81"/>
     </row>
     <row r="21" spans="1:4" ht="47.25" customHeight="1">
       <c r="A21" s="11" t="str">
         <f>IFERROR(VLOOKUP(B9,'FOC Approval Matrix 核准矩陣  '!B:E,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
+      <c r="B21" s="68"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="81"/>
     </row>
     <row r="22" spans="1:4" ht="17.25">
       <c r="A22" s="12"/>
       <c r="B22" s="13"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="83"/>
     </row>
     <row r="23" spans="1:4" ht="15.75">
       <c r="A23" s="14"/>
@@ -2658,7 +2664,7 @@
       <c r="D23" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="A2:D2"/>
@@ -2668,6 +2674,7 @@
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="C19:D22"/>
   </mergeCells>
   <phoneticPr fontId="16" type="noConversion"/>
   <conditionalFormatting sqref="B6:B8">
